--- a/geesun_dog_urdf/geesun-dog/lingsi_d30w/urdf/D30W关节电气参数.xlsx
+++ b/geesun_dog_urdf/geesun-dog/lingsi_d30w/urdf/D30W关节电气参数.xlsx
@@ -29,7 +29,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
   <si>
-    <t>D30W关节电气参数</t>
+    <r>
+      <t>D30W</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关节电气参数</t>
+    </r>
   </si>
   <si>
     <t>输出端参数</t>
@@ -44,10 +56,86 @@
     <t>角度范围（rad）</t>
   </si>
   <si>
-    <t>角速度范围（rad/s）</t>
-  </si>
-  <si>
-    <t>扭矩范围（Nm）</t>
+    <r>
+      <t>角速度范围</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>velocity</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>rad/s</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>扭矩</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>effort</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>范围（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Nm</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
   </si>
   <si>
     <t>KP最大值</t>
@@ -62,7 +150,7 @@
     <t>电流环带宽</t>
   </si>
   <si>
-    <t>LS100_WLA 髋关节</t>
+    <t>LS100_WLA 髋关节，Hip（髋）</t>
   </si>
   <si>
     <t>40</t>
@@ -86,10 +174,10 @@
     <t>1000</t>
   </si>
   <si>
-    <t>LS100_WLH大腿</t>
-  </si>
-  <si>
-    <t>LS100_WLK小腿</t>
+    <t>LS100_WLH大腿，Thigh（大腿）</t>
+  </si>
+  <si>
+    <t>LS100_WLK小腿，Calf（小腿）</t>
   </si>
   <si>
     <t>200</t>
@@ -114,12 +202,176 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Nimbus Roman No9 L"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -132,159 +384,8 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="微软雅黑"/>
+      <name val="Nimbus Roman No9 L"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
@@ -762,13 +863,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1171,10 +1275,10 @@
       <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="3" t="s">

--- a/geesun_dog_urdf/geesun-dog/lingsi_d30w/urdf/D30W关节电气参数.xlsx
+++ b/geesun_dog_urdf/geesun-dog/lingsi_d30w/urdf/D30W关节电气参数.xlsx
@@ -27,9 +27,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="29">
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Nimbus Roman No9 L"/>
+        <charset val="134"/>
+      </rPr>
       <t>D30W</t>
     </r>
     <r>
@@ -162,10 +169,10 @@
     <t>120</t>
   </si>
   <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>最大500,推荐200</t>
+  </si>
+  <si>
+    <t>最大5,推荐5</t>
   </si>
   <si>
     <t>60</t>
@@ -190,6 +197,18 @@
   </si>
   <si>
     <t>14</t>
+  </si>
+  <si>
+    <t>最大500,厂家说没有此设置</t>
+  </si>
+  <si>
+    <t>最大5,推荐3</t>
+  </si>
+  <si>
+    <t>27 URDF</t>
+  </si>
+  <si>
+    <t>72 URDF</t>
   </si>
 </sst>
 </file>
@@ -202,7 +221,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,13 +243,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -373,18 +385,18 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Nimbus Roman No9 L"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Nimbus Roman No9 L"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -718,161 +730,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1223,8 +1232,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelRow="6"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="22.0666666666667" customWidth="1"/>
     <col min="2" max="2" width="5" customWidth="1"/>
@@ -1232,7 +1241,8 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="7" max="7" width="18.825" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1275,10 +1285,10 @@
       <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -1410,16 +1420,24 @@
         <v>24</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="5:6">
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
